--- a/project1-green-bond-analysis/Green_Bond_Market_Analysis.xlsx
+++ b/project1-green-bond-analysis/Green_Bond_Market_Analysis.xlsx
@@ -3825,14 +3825,14 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>RESULT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Framework and sources only — no empirical estimate is claimed here. The point of specifying it against published sovereign twin data is that it is executable without any paid data subscription, which the earlier terminal-based version of this sheet was not.</t>
+          <t>Measured on this framework: -1.50bps pooled across all nine German green twin pairs, 8,094 paired daily observations from September 2020 to October 2026 (HAC standard error 0.052, t = -28.7), negative on 99.8% of days, and compressed roughly 80% since 2021. German sovereign only. Reproduce with scripts/fetch_bund_yields.py then scripts/greenium.py; the full write-up is in brief/Green_Bond_Market_Brief.pdf. Every input is published free by the issuer — no paid data subscription is involved, which the earlier terminal-based version of this sheet required.</t>
         </is>
       </c>
     </row>

--- a/project1-green-bond-analysis/Green_Bond_Market_Analysis.xlsx
+++ b/project1-green-bond-analysis/Green_Bond_Market_Analysis.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0. Summary Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1. Data Quality" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2. Annual Issuance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3. Geography" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4. Sector Breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5. Theme Evolution" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="6. SLB Analysis" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7. Greenium Framework" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. Summary Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Data Quality" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Annual Issuance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Geography" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Sector Breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Theme Evolution" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. SLB Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Greenium Framework" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -214,13 +214,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -244,7 +244,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -272,8 +272,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -299,8 +299,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -326,13 +326,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -355,14 +355,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -390,8 +390,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -417,8 +417,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -444,13 +444,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -474,7 +474,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -526,13 +526,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -556,7 +556,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -608,13 +608,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -637,14 +637,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -672,8 +672,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -699,8 +699,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -726,7 +726,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -741,9 +741,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -763,9 +763,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -775,7 +775,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -790,9 +790,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -802,7 +802,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -817,9 +817,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -829,7 +829,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -844,9 +844,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>SLBs are 15% of deals but only 3% of volume — many small transactions. SLB share of annual volume reached 11.8% in 2024, up from nil before 2021.</t>
+          <t>SLBs are 15% of deals but only 3% of volume — many small transactions. SLB share of annual volume reached 11.8% in 2024, up from almost nothing before 2021 (a single 2015 record, flagged on the Data Quality sheet as mislabelled, aside).</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Sovereign dominance</t>
+          <t>Sovereign share (sample)</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Sovereign issuers are 82% of volume across 448 deals — government programmes, not corporate issuance, are what scaled this market.</t>
+          <t>Sovereign issuers are 82% of this sample's volume across 448 deals. That reflects the selection of a newsflow extract, not the market: CBI's Sustainable Debt Market Summary Q3 2024 puts sovereigns at $630.5bn of $5.4tn cumulative aligned volume, about 11.6%.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>No terminal data is used. Sheet 7 sets out the academic evidence and a matched-pair framework built on freely published sovereign green/conventional 'twin' bond yields — see that sheet for sources.</t>
+          <t>No terminal data is used. Sheet 7 sets out the academic evidence and a matched-pair framework built on issuer-published sovereign green/conventional 'twin' bond yields — see that sheet for sources.</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Ranked by volume rather than deal count: China leads on deal count (68) but ranks 6th by volume, because its issuance in this dataset is many small bank deals while European volume is concentrated in large sovereign programmes. Volume is the more meaningful ranking for market size.</t>
+          <t>Ranked by volume rather than deal count: China leads on deal count (68) but ranks 6th by volume, because its issuance in this dataset is many small bank deals while European volume is concentrated in large sovereign programmes. Volume is the more meaningful ranking for where capital moved in this sample.</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Global primary market</t>
+          <t>Global, primary and secondary</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Coarsened exact matching</t>
+          <t>Propensity-score and coarsened exact matching</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US corporates</t>
+          <t>Global corporates, at issuance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Matching + event study</t>
+          <t>Fixed-effects panel regression</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Panizza et al. (2025)</t>
+          <t>Panizza, Shi, Weder di Mauro &amp; Gulati (2025)</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
@@ -3565,17 +3565,17 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Sovereign bonds</t>
+          <t>Sovereign and sovereign-backed, secondary</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>−5 to −8</t>
+          <t>≈ −2 advanced, ≈ −13 emerging</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Synthetic control</t>
+          <t>332 matched pairs</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Banque de France (2025)</t>
+          <t>Pietsch &amp; Salakhova (2025)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -3595,22 +3595,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eurozone</t>
+          <t>Euro area, secondary</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>−2 to −13</t>
+          <t>≈ −3.7 average</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Propensity-score matching</t>
+          <t>k-prototypes matching</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Working Paper 1010</t>
+          <t>Banque de France Working Paper 1010</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>5. Test whether the mean difference is distinguishable from zero (t-test on the daily series, Newey-West standard errors for autocorrelation).</t>
+          <t>5. Test whether the mean difference is distinguishable from zero. The daily spread stays autocorrelated for months and pairs share dates, so use a panel HAC (Driscoll-Kraay) standard error with a long bandwidth, and check the sign against a t-test across pair means.</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Measured on this framework: -1.50bps pooled across all nine German green twin pairs, 8,094 paired daily observations from September 2020 to October 2026 (HAC standard error 0.052, t = -28.7), negative on 99.8% of days, and compressed roughly 80% since 2021. German sovereign only. Reproduce with scripts/fetch_bund_yields.py then scripts/greenium.py; the full write-up is in brief/Green_Bond_Market_Brief.pdf. Every input is published free by the issuer — no paid data subscription is involved, which the earlier terminal-based version of this sheet required.</t>
+          <t>Measured on this framework: -1.50bps pooled across all nine German green twin pairs, 8,094 paired daily observations from September 2020 to October 2026 (Driscoll-Kraay standard error 0.330 with a 250-day bandwidth, t = -4.5; an earlier 10-lag calculation on the stacked series overstated this as t = -28.7), negative on 99.8% of days, and down from -4.71bps in 2021 to -0.76bps in 2025. German sovereign only. Reproduce with scripts/fetch_bund_yields.py then scripts/greenium.py; the full write-up is in brief/Green_Bond_Market_Brief.pdf. Every input is published free by the issuer — no paid data subscription is involved, which the earlier terminal-based version of this sheet required.</t>
         </is>
       </c>
     </row>

--- a/project1-green-bond-analysis/Green_Bond_Market_Analysis.xlsx
+++ b/project1-green-bond-analysis/Green_Bond_Market_Analysis.xlsx
@@ -3828,7 +3828,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Measured on this framework: -1.50bps pooled across all nine German green twin pairs, 8,094 paired daily observations from September 2020 to October 2026 (Driscoll-Kraay standard error 0.330 with a 250-day bandwidth, t = -4.5; an earlier 10-lag calculation on the stacked series overstated this as t = -28.7), negative on 99.8% of days, and down from -4.71bps in 2021 to -0.76bps in 2025. German sovereign only. Reproduce with scripts/fetch_bund_yields.py then scripts/greenium.py; the full write-up is in brief/Green_Bond_Market_Brief.pdf. Every input is published free by the issuer — no paid data subscription is involved, which the earlier terminal-based version of this sheet required.</t>
+          <t>Measured on this framework: -1.50bps pooled across all nine German green twin pairs, 8,094 paired daily observations from September 2020 to October 2026 (Driscoll-Kraay standard error 0.330 with a 250-day bandwidth, t = -4.5; an earlier 10-lag calculation on the stacked series overstated this as t = -28.7), negative on 99.8% of pair-date observations and on every date's cross-pair average, and down from -4.71bps in 2021 to -0.76bps in 2025. German sovereign only. Reproduce with scripts/fetch_bund_yields.py then scripts/greenium.py; the full write-up is in brief/Green_Bond_Market_Brief.pdf. Every input is published free by the issuer — no paid data subscription is involved, which the earlier terminal-based version of this sheet required.</t>
         </is>
       </c>
     </row>
